--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60a4d21753af40f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R0ad1b13246fe468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R9516a01b25564c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R122473dbc519451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rffcfd9be826b42f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R9b3cdb8892a14d1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -578,6 +578,40 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>ColorTiming loading overlay</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>ColorTiming/Game/Loading</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H8" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R122473dbc519451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rffcfd9be826b42f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R9b3cdb8892a14d1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9391634456c4ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R275d074fb411455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R7698ea822b124900"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,13 +604,27 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
-      <x:c r="G9"/>
-      <x:c r="H9"/>
+      <x:c r="B9" t="n">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>ColorTiming battle HUD</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>ColorTiming/Game/BattleHud</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9391634456c4ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R275d074fb411455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R7698ea822b124900"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R25b2885d357e4ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R0688f3509d00408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R0ec619d69ee141eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -518,7 +518,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" t="str">
-        <x:v>ColorTiming/Game/Esc</x:v>
+        <x:v>ColorTiming/Game/PauseMenu</x:v>
       </x:c>
       <x:c r="F5" s="2" t="b">
         <x:v>0</x:v>

--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R25b2885d357e4ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R0688f3509d00408a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R0ec619d69ee141eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a9385e9a7ad4347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rbee7fff9a281488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="Refaa7656e00f4e18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -626,6 +626,30 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10" t="n">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>ColorTiming battle tutorial</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>ColorTiming/Game/BattleTutorial</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H10" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
